--- a/quiz/old-quiz/DST1.1.xlsx
+++ b/quiz/old-quiz/DST1.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_5 QUESTION DATABASE\Web Database\_0 Access Database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\firebrigade\wp-content\plugins\techiquiz\quiz\old-quiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CADD559-064E-4743-9484-12CBC41CC9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC3464E-D461-4317-850A-057481810976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F054DF8D-A09E-430C-AA09-6416AFCA4198}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F054DF8D-A09E-430C-AA09-6416AFCA4198}"/>
   </bookViews>
   <sheets>
     <sheet name="DST1" sheetId="1" r:id="rId1"/>
@@ -1465,7 +1465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1526,6 +1526,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4290,9 +4293,10 @@
       <c r="J66" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="L66" s="1" t="s">
+      <c r="K66" s="21" t="s">
         <v>18</v>
       </c>
+      <c r="L66" s="1"/>
       <c r="M66"/>
     </row>
     <row r="67" spans="1:13" s="3" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
